--- a/results/Int Task Remove ACC -0.6/Rando_9_permute.xlsx
+++ b/results/Int Task Remove ACC -0.6/Rando_9_permute.xlsx
@@ -440,587 +440,587 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.6411449697588089</v>
+        <v>0.6007191093448973</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>scl_min</t>
+          <t>bvp_rms</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.6438524122468433</v>
+        <v>0.6043586249488149</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hrv_min</t>
+          <t>bvp_pct_95</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.6352966053339957</v>
+        <v>0.613445750458149</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>bvp_sum</t>
+          <t>bvp_n_sign_changes</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.6349750619256356</v>
+        <v>0.6135855446435164</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>scr_kurtosis</t>
+          <t>scr_skewness</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.6355156106303996</v>
+        <v>0.6242057072276782</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>scr_ptp</t>
+          <t>scr_mean</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.6402968067181762</v>
+        <v>0.6292384657210561</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>bvp_rms</t>
+          <t>hrv_entropy</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.6416529613543758</v>
+        <v>0.6281526693473138</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>hrv_rms</t>
+          <t>scr_n_sign_changes</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.6468721680349603</v>
+        <v>0.6281526693473138</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>scr_svd_entropy</t>
+          <t>scr_perm_entropy</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.6470911733313642</v>
+        <v>0.6262328068255811</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>scl_n_sign_changes</t>
+          <t>hrv_std</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.6490576898549363</v>
+        <v>0.629690573206506</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>scl_std</t>
+          <t>scr_iqr_5_95</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.6648970591196826</v>
+        <v>0.6210089011807826</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>scl_n_above_mean</t>
+          <t>scl_rms</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.6648551040820574</v>
+        <v>0.6349889909981271</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>bvp_kurtosis</t>
+          <t>scr_n_above_mean</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.6643937664883297</v>
+        <v>0.6361726265196115</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>scr_lineintegral</t>
+          <t>scl_pct_5</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.6446072672837972</v>
+        <v>0.6698553054662379</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>scr_n_below_mean</t>
+          <t>hrv_iqr</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.648782632628265</v>
+        <v>0.6669288576817995</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>scr_sum</t>
+          <t>scr_pct_5</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.6362145815572366</v>
+        <v>0.6673807973470991</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>hrv_peaks</t>
+          <t>scl_min</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.6372164678557284</v>
+        <v>0.6837142291349207</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>scr_std</t>
+          <t>bvp_max</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.6360887164443609</v>
+        <v>0.7027645013392048</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_below_mean</t>
+          <t>scr_svd_entropy</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.6221507494847921</v>
+        <v>0.7037338305284992</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>scr_max</t>
+          <t>scl_peaks</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.6127234525303922</v>
+        <v>0.7042557511965577</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>scl_energy</t>
+          <t>hrv_kurtosis</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.6215821748148944</v>
+        <v>0.7004205572971558</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_95</t>
+          <t>scr_iqr</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.6425848666501084</v>
+        <v>0.6861187562513006</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>scl_rms</t>
+          <t>scr_rms</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.6716216125502621</v>
+        <v>0.7034213494082662</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>scr_n_above_mean</t>
+          <t>scl_skewness</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.6634898871577308</v>
+        <v>0.7016132551067671</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_95</t>
+          <t>bvp_mean</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.6587926011452048</v>
+        <v>0.7007697910303485</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr_5_95</t>
+          <t>scl_mean</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.6691986252173271</v>
+        <v>0.7200296706026086</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>hrv_std</t>
+          <t>scl_std</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.6708576952251811</v>
+        <v>0.7244054132067745</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_5</t>
+          <t>scl_energy</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.6749538494586123</v>
+        <v>0.7267354281763321</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>scl_lineintegral</t>
+          <t>bvp_std</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.6797909296565057</v>
+        <v>0.7121030214339896</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_95</t>
+          <t>scl_kurtosis</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.7030541589189697</v>
+        <v>0.7167257952996933</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>scr_entropy</t>
+          <t>hrv_rms</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.7036180346246534</v>
+        <v>0.6993857782491659</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>scl_perm_entropy</t>
+          <t>hrv_n_sign_changes</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.6983382448697379</v>
+        <v>0.6993857782491659</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>hrv_ptp</t>
+          <t>scl_iqr_5_95</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.7027655082601079</v>
+        <v>0.7333993985325806</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>bvp_max</t>
+          <t>hrv_perm_entropy</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.6890885016345683</v>
+        <v>0.7318522645651109</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>scl_svd_entropy</t>
+          <t>bvp_min</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.7047274936396163</v>
+        <v>0.7345457779806537</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>scr_skewness</t>
+          <t>scr_sum</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.7024580617443899</v>
+        <v>0.7317171693439575</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_above_mean</t>
+          <t>scl_ptp</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.7020945632984044</v>
+        <v>0.7265491478092758</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>scl_sum</t>
+          <t>hrv_iqr_5_95</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.7277759131094389</v>
+        <v>0.7114460055447778</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>bvp_min</t>
+          <t>bvp_ptp</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.7310052762655318</v>
+        <v>0.7139532385932643</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr</t>
+          <t>hrv_n_below_mean</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.7434100383301223</v>
+        <v>0.7144565312246172</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr_5_95</t>
+          <t>scl_n_sign_changes</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.7408096650981076</v>
+        <v>0.7121265162550598</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>scl_peaks</t>
+          <t>bvp_perm_entropy</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.7408096650981076</v>
+        <v>0.6929552457222643</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>bvp_svd_entropy</t>
+          <t>bvp_pct_5</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.741844276325947</v>
+        <v>0.72606498667508</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr</t>
+          <t>hrv_min</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.7324077492632696</v>
+        <v>0.7347840825943652</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>hrv_entropy</t>
+          <t>hrv_energy</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.7311774597399459</v>
+        <v>0.7304828521370218</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>bvp_skewness</t>
+          <t>scr_kurtosis</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.7276265531754929</v>
+        <v>0.7332928327370124</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>scr_peaks</t>
+          <t>hrv_max</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.7276265531754929</v>
+        <v>0.6826247407178675</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>bvp_energy</t>
+          <t>hrv_svd_entropy</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.7124024125824836</v>
+        <v>0.6741342158435648</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_5</t>
+          <t>scl_lineintegral</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.6656253985728574</v>
+        <v>0.6652102115205176</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>scr_energy</t>
+          <t>hrv_mean</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.6817116312789909</v>
+        <v>0.67454453611154</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>scr_n_sign_changes</t>
+          <t>hrv_n_above_mean</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.6817116312789909</v>
+        <v>0.676674173821399</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>hrv_svd_entropy</t>
+          <t>bvp_svd_entropy</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.6785146574119447</v>
+        <v>0.6772380495270829</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>bvp_mean</t>
+          <t>scl_pct_95</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.6808027173438769</v>
+        <v>0.6764504695607811</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_5</t>
+          <t>bvp_sum</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.6825409984627675</v>
+        <v>0.6764504695607811</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>hrv_kurtosis</t>
+          <t>scl_sum</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.6749125657015889</v>
+        <v>0.6830630869509764</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_above_mean</t>
+          <t>scl_perm_entropy</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.600151373775752</v>
+        <v>0.675094482744732</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>scl_ptp</t>
+          <t>scl_iqr</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.6010740489632072</v>
+        <v>0.6709518423296121</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_sign_changes</t>
+          <t>hrv_peaks</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.6010740489632072</v>
+        <v>0.6684820331746874</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>scl_entropy</t>
+          <t>hrv_ptp</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.6065167920842591</v>
+        <v>0.6692603830327115</v>
       </c>
     </row>
     <row r="61">
@@ -1030,107 +1030,107 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.5861246299565681</v>
+        <v>0.6458019789352147</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr</t>
+          <t>scr_peaks</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.6177009981942552</v>
+        <v>0.6458019789352147</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>scl_kurtosis</t>
+          <t>scr_ptp</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.6175192489712624</v>
+        <v>0.6388678181366593</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr_5_95</t>
+          <t>bvp_lineintegral</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.6677312058213454</v>
+        <v>0.6110429015432741</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>bvp_ptp</t>
+          <t>scr_lineintegral</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.6874987413488712</v>
+        <v>0.5720618048050266</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>hrv_sum</t>
+          <t>hrv_lineintegral</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.6980868502842874</v>
+        <v>0.5914057622726876</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>hrv_lineintegral</t>
+          <t>scl_entropy</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.6713431989205808</v>
+        <v>0.5865500540380885</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>scr_rms</t>
+          <t>bvp_skewness</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.6786406903449711</v>
+        <v>0.5726726701528506</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_sign_changes</t>
+          <t>bvp_n_below_mean</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.6853232887379253</v>
+        <v>0.6008097322261678</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>hrv_energy</t>
+          <t>scr_entropy</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.5957346830548638</v>
+        <v>0.6008097322261678</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>bvp_std</t>
+          <t>hrv_pct_95</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.5814100584685404</v>
+        <v>0.5349220307580772</v>
       </c>
     </row>
     <row r="72">
@@ -1140,163 +1140,163 @@
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.5852126952587451</v>
+        <v>0.5400806543643308</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>scr_mean</t>
+          <t>hrv_sum</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.5896815780464392</v>
+        <v>0.5075258946492224</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>bvp_perm_entropy</t>
+          <t>scr_std</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.5608967301921877</v>
+        <v>0.5069620189435385</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>scr_min</t>
+          <t>scr_max</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.5608967301921877</v>
+        <v>0.5087281582074122</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr_5_95</t>
+          <t>hrv_pct_5</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.5420421362833878</v>
+        <v>0.5013048016701461</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>bvp_lineintegral</t>
+          <t>bvp_kurtosis</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.5559336170612678</v>
+        <v>0.5010438413361169</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>hrv_perm_entropy</t>
+          <t>scl_svd_entropy</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.5577603393994723</v>
+        <v>0.5010438413361169</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>scl_max</t>
+          <t>bvp_energy</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.5654399573065537</v>
+        <v>0.5007828810020877</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr</t>
+          <t>bvp_entropy</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.5625834905248743</v>
+        <v>0.5007828810020877</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>hrv_mean</t>
+          <t>scr_energy</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.5864332512133397</v>
+        <v>0.5010438413361169</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_below_mean</t>
+          <t>scr_n_below_mean</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.5915126637085568</v>
+        <v>0.5010438413361169</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>bvp_entropy</t>
+          <t>bvp_n_above_mean</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.5915126637085568</v>
+        <v>0.5007222979277568</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>scr_perm_entropy</t>
+          <t>hrv_skewness</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.5739585081459901</v>
+        <v>0.5007828810020877</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>hrv_max</t>
+          <t>scr_min</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.521687565869409</v>
+        <v>0.5007828810020877</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>bvp_peaks</t>
+          <t>bvp_iqr</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.5010438413361169</v>
+        <v>0.5007222979277568</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>scl_mean</t>
+          <t>scl_max</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.5004613375937276</v>
+        <v>0.5007828810020877</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>hrv_skewness</t>
+          <t>scl_n_above_mean</t>
         </is>
       </c>
       <c r="B88" t="n">
@@ -1306,21 +1306,21 @@
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_5</t>
+          <t>bvp_iqr_5_95</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0.5002609603340292</v>
+        <v>0.5010438413361169</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>scl_skewness</t>
+          <t>bvp_peaks</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.5002609603340292</v>
+        <v>0.5</v>
       </c>
     </row>
   </sheetData>
